--- a/Table7_Protocol.xlsx
+++ b/Table7_Protocol.xlsx
@@ -1,42 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="BP1 - Non-OECD Europe" sheetId="1" r:id="rId1"/>
-    <sheet name="BP2 - OECD Europe" sheetId="2" r:id="rId2"/>
-    <sheet name="Notes" sheetId="3" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BP1 - Non-OECD Europe" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BP2 - OECD Europe" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -55,16 +56,83 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -352,11 +420,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" customFormat="1" s="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Effect Size</t>
@@ -428,11 +500,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" customFormat="1" s="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Effect Size</t>
@@ -504,11 +580,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" customFormat="1" s="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Scenario</t>
@@ -528,7 +608,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>"Best Practice" predictions are derived from the CHE estimates in Table 6, Panel A. Predictions are evaluated at se(z) = 0, SC1_Cognitive = 1, SC1_Structural = 0, SC1_Other = 0 (reference), DV_GrowthRate = 1, DV_GDPLevel = 0 (reference), PubYear = 2010.4 (sample mean), Published = 1, LaggedDV = 0, LaggedSC = 0, NumberSCVars = 1, Endog_IV = 1, Endog_FE = 1, CityLevel = 0, RegionLevel = 0, CountryLevel = 1, PanelData = 1, Reg_OECDEurope = 0, Reg_US = 0, Reg_Africa = 0, Reg_Asia = 0.</t>
+          <t>"Best Practice" predictions are derived from the CHE estimates in Table 6, Panel A. Predictions are evaluated at se(z) = 0, SC1_Cognitive = 1, SC1_Structural = 0, SC1_Other = 0 (reference), DV_GrowthRate = 1, DV_GDPLevel = 0 (reference), PubYear = 2010.4 (sample mean), Published = 1, LaggedDV = 0, LaggedSC = 0, NumberSCVars = 1, Endog_IV = 1, Endog_FE = 1, CityLevel = 0, RegionLevel = 0, CountryLevel = 1, PanelData = 1, Reg_OECDEurope = 0, Reg_US = 0, Reg_Africa = 0, Reg_Asia = 0. The covariance matrix used to fit this model assumes a within-study correlation of rho = 0.500 (Section 4).</t>
         </is>
       </c>
     </row>
@@ -540,7 +620,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>"Best Practice" predictions are derived from the CHE estimates in Table 6, Panel A. Predictions are evaluated at se(z) = 0, SC1_Cognitive = 1, SC1_Structural = 0, SC1_Other = 0 (reference), DV_GrowthRate = 1, DV_GDPLevel = 0 (reference), PubYear = 2010.4 (sample mean), Published = 1, LaggedDV = 0, LaggedSC = 0, NumberSCVars = 1, Endog_IV = 1, Endog_FE = 1, CityLevel = 0, RegionLevel = 0, CountryLevel = 1, PanelData = 1, Reg_OECDEurope = 1, Reg_US = 0, Reg_Africa = 0, Reg_Asia = 0.</t>
+          <t>"Best Practice" predictions are derived from the CHE estimates in Table 6, Panel A. Predictions are evaluated at se(z) = 0, SC1_Cognitive = 1, SC1_Structural = 0, SC1_Other = 0 (reference), DV_GrowthRate = 1, DV_GDPLevel = 0 (reference), PubYear = 2010.4 (sample mean), Published = 1, LaggedDV = 0, LaggedSC = 0, NumberSCVars = 1, Endog_IV = 1, Endog_FE = 1, CityLevel = 0, RegionLevel = 0, CountryLevel = 1, PanelData = 1, Reg_OECDEurope = 1, Reg_US = 0, Reg_Africa = 0, Reg_Asia = 0. The covariance matrix used to fit this model assumes a within-study correlation of rho = 0.500 (Section 4).</t>
         </is>
       </c>
     </row>

--- a/Table7_Protocol.xlsx
+++ b/Table7_Protocol.xlsx
@@ -1,43 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BP1 - Non-OECD Europe" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BP2 - OECD Europe" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BP1 - Non-OECD Europe" sheetId="1" r:id="rId1"/>
+    <sheet name="BP2 - OECD Europe" sheetId="2" r:id="rId2"/>
+    <sheet name="Notes" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -56,83 +55,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -420,15 +352,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" customFormat="1" s="1">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Effect Size</t>
@@ -500,15 +428,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" customFormat="1" s="1">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Effect Size</t>
@@ -580,15 +504,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" customFormat="1" s="1">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Scenario</t>
